--- a/mapping/SB_DWH/Mapping_FCT_CLOS_APPLICATION.xlsx
+++ b/mapping/SB_DWH/Mapping_FCT_CLOS_APPLICATION.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -167,8 +167,16 @@
     </font>
     <font>
       <name val="Times New Roman"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
       <b val="1"/>
-      <color theme="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -239,7 +247,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -400,7 +408,10 @@
     <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -707,15 +718,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16"/>
   <cols>
     <col width="34.33203125" customWidth="1" style="19" min="1" max="1"/>
     <col width="19" customWidth="1" style="19" min="2" max="2"/>
     <col width="30.6640625" bestFit="1" customWidth="1" style="15" min="3" max="3"/>
-    <col width="36.6640625" bestFit="1" customWidth="1" style="16" min="4" max="4"/>
-    <col width="59.5" customWidth="1" style="19" min="5" max="5"/>
-    <col width="59.1640625" customWidth="1" style="16" min="6" max="6"/>
+    <col width="69.1640625" customWidth="1" style="16" min="4" max="4"/>
+    <col width="90.1640625" customWidth="1" style="19" min="5" max="5"/>
+    <col width="90.1640625" customWidth="1" style="16" min="6" max="6"/>
     <col width="9.1640625" customWidth="1" style="19" min="7" max="16384"/>
   </cols>
   <sheetData>
@@ -735,7 +746,6 @@
           <t>NG_SB_CLOS_EXTTABLE AS A</t>
         </is>
       </c>
-      <c r="F1" s="52" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
@@ -753,7 +763,6 @@
           <t>DIM_CLOS_APPLICATION AS B</t>
         </is>
       </c>
-      <c r="F2" s="52" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="21" t="inlineStr">
@@ -771,7 +780,6 @@
           <t>NG_SB_CLOS_ENTRY_EXIT AS C</t>
         </is>
       </c>
-      <c r="F3" s="52" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
@@ -789,7 +797,6 @@
           <t>DIM_CLOS_WORKSTEP_DECISION AS D</t>
         </is>
       </c>
-      <c r="F4" s="52" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="13" t="n"/>
@@ -798,7 +805,6 @@
           <t>NG_SB_CLOS_CUST_INFO AS E</t>
         </is>
       </c>
-      <c r="F5" s="52" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="13" t="n"/>
@@ -807,7 +813,6 @@
           <t>DIM_CLOS_PRODUCT AS F</t>
         </is>
       </c>
-      <c r="F6" s="52" t="n"/>
     </row>
     <row r="7" hidden="1">
       <c r="A7" s="13" t="n"/>
@@ -816,7 +821,6 @@
           <t>DIM_LOS_COMPANY AS G</t>
         </is>
       </c>
-      <c r="F7" s="52" t="n"/>
     </row>
     <row r="8" hidden="1">
       <c r="A8" s="13" t="n"/>
@@ -825,7 +829,6 @@
           <t>NG_SB_CLOS_CUST_INFO_LEGAL AS H</t>
         </is>
       </c>
-      <c r="F8" s="53" t="n"/>
     </row>
     <row r="9" hidden="1">
       <c r="A9" s="13" t="n"/>
@@ -834,7 +837,6 @@
           <t>DIM_CLOS_CUSTOMER AS I</t>
         </is>
       </c>
-      <c r="F9" s="52" t="n"/>
     </row>
     <row r="10" hidden="1">
       <c r="A10" s="13" t="n"/>
@@ -843,7 +845,6 @@
           <t>NG_SB_CLOS_CREDITINFO_COMM AS J</t>
         </is>
       </c>
-      <c r="F10" s="52" t="n"/>
     </row>
     <row r="11" hidden="1">
       <c r="A11" s="13" t="n"/>
@@ -852,7 +853,6 @@
           <t>NG_SB_CLOS_CREDITINFO_CD AS K</t>
         </is>
       </c>
-      <c r="F11" s="52" t="n"/>
     </row>
     <row r="12" hidden="1">
       <c r="A12" s="13" t="n"/>
@@ -861,7 +861,6 @@
           <t>WFINSTRUMENTTABLE AS L</t>
         </is>
       </c>
-      <c r="F12" s="52" t="n"/>
     </row>
     <row r="13" hidden="1">
       <c r="A13" s="13" t="n"/>
@@ -870,12 +869,10 @@
           <t>NG_SB_CLOS_CHANGEREQ AS M</t>
         </is>
       </c>
-      <c r="F13" s="52" t="n"/>
     </row>
     <row r="14" hidden="1">
       <c r="A14" s="13" t="n"/>
       <c r="E14" s="53" t="n"/>
-      <c r="F14" s="53" t="n"/>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="1" t="inlineStr">
@@ -903,9 +900,8 @@
           <t>How to mapping CLOS</t>
         </is>
       </c>
-      <c r="F15" s="1" t="n"/>
-    </row>
-    <row r="16" ht="51" customHeight="1">
+    </row>
+    <row r="16">
       <c r="A16" s="6" t="n"/>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="7" t="n"/>
@@ -915,9 +911,8 @@
         </is>
       </c>
       <c r="E16" s="6" t="n"/>
-      <c r="F16" s="12" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1">
+    </row>
+    <row r="17" ht="45" customHeight="1">
       <c r="A17" s="28" t="inlineStr">
         <is>
           <t>DAYID</t>
@@ -933,17 +928,16 @@
           <t>Ngày dữ liệu</t>
         </is>
       </c>
-      <c r="D17" s="27" t="inlineStr">
+      <c r="D17" s="54" t="inlineStr">
         <is>
           <t>PK — Driving: NG_SB_CLOS_EXTTABLE. Ngày dữ liệu, dạng số YYYYMMDD. Full snapshot: mọi WI_NAME còn hiệu lực trên EXTTABLE sinh dòng ở MỌI DAYID</t>
         </is>
       </c>
-      <c r="E17" s="28" t="inlineStr">
+      <c r="E17" s="31" t="inlineStr">
         <is>
           <t>v_batch_date</t>
         </is>
       </c>
-      <c r="F17" s="28" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="28" t="inlineStr">
@@ -961,19 +955,18 @@
           <t>Khóa tới hồ sơ tín dụng</t>
         </is>
       </c>
-      <c r="D18" s="27" t="inlineStr">
-        <is>
-          <t>Khóa ngoại — tra DIM_CLOS_APPLICATION [CẦN REVIEW] Mặc định -1 nếu không khớp</t>
-        </is>
-      </c>
-      <c r="E18" s="28" t="inlineStr">
+      <c r="D18" s="54" t="inlineStr">
+        <is>
+          <t>Khóa ngoại — tra DIM_CLOS_APPLICATION</t>
+        </is>
+      </c>
+      <c r="E18" s="31" t="inlineStr">
         <is>
           <t>B.DIMENSION_KEY</t>
         </is>
       </c>
-      <c r="F18" s="28" t="n"/>
-    </row>
-    <row r="19" ht="30" customHeight="1">
+    </row>
+    <row r="19" ht="75" customHeight="1">
       <c r="A19" s="28" t="inlineStr">
         <is>
           <t>WORKSTEP_DECISION_SK</t>
@@ -989,19 +982,18 @@
           <t>Khóa tới bước/quyết định gần nhất</t>
         </is>
       </c>
-      <c r="D19" s="27" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_CLOS_WORKSTEP_DECISION (gộp từ LAST_WORKSTEP_SK+LAST_DECISION_SK) của sự kiện hoàn tất gần nhất — đổi tên từ LAST_WORKSTEP_DECISION_SK (review 2026-10-04, theo yêu cầu người dùng). Lookup theo cặp WORKSTEP_CODE+DECISION_CODE của sự kiện hoàn tất gần nhất [CẦN REVIEW] Mặc định -1</t>
-        </is>
-      </c>
-      <c r="E19" s="28" t="inlineStr">
+      <c r="D19" s="54" t="inlineStr">
+        <is>
+          <t>Khóa tới DIM_CLOS_WORKSTEP_DECISION (gộp từ LAST_WORKSTEP_SK+LAST_DECISION_SK) của sự kiện hoàn tất gần nhất — đổi tên từ LAST_WORKSTEP_DECISION_SK. Lookup theo cặp WORKSTEP_CODE+DECISION_CODE của sự kiện hoàn tất gần nhất</t>
+        </is>
+      </c>
+      <c r="E19" s="31" t="inlineStr">
         <is>
           <t>D.DIMENSION_KEY</t>
         </is>
       </c>
-      <c r="F19" s="28" t="n"/>
-    </row>
-    <row r="20" ht="15" customFormat="1" customHeight="1" s="20">
+    </row>
+    <row r="20" ht="45" customHeight="1">
       <c r="A20" s="28" t="inlineStr">
         <is>
           <t>PRODUCTLINE_SK</t>
@@ -1017,19 +1009,18 @@
           <t>Khóa layer Product Line</t>
         </is>
       </c>
-      <c r="D20" s="27" t="inlineStr">
-        <is>
-          <t>Khóa ngoại — tra DIM_CLOS_PRODUCT (layer Product Line). Thay cho PRODUCT_SK cũ — DIM_CLOS_PRODUCT tách 2 layer SCD2 độc lập (Product Line/Sub Product) [CẦN REVIEW] Mặc định -1 nếu không khớp</t>
-        </is>
-      </c>
-      <c r="E20" s="28" t="inlineStr">
+      <c r="D20" s="54" t="inlineStr">
+        <is>
+          <t>Khóa ngoại — tra DIM_CLOS_PRODUCT (layer Product Line). Thay cho PRODUCT_SK cũ — DIM_CLOS_PRODUCT tách 2 layer SCD2 độc lập (Product Line/Sub Product)</t>
+        </is>
+      </c>
+      <c r="E20" s="31" t="inlineStr">
         <is>
           <t>F.PRODUCTLINE_SK</t>
         </is>
       </c>
-      <c r="F20" s="28" t="n"/>
-    </row>
-    <row r="21" ht="15" customHeight="1">
+    </row>
+    <row r="21" ht="75" customHeight="1">
       <c r="A21" s="28" t="inlineStr">
         <is>
           <t>SUB_PRODUCT_SK</t>
@@ -1045,19 +1036,18 @@
           <t>Khóa layer Sub Product</t>
         </is>
       </c>
-      <c r="D21" s="27" t="inlineStr">
-        <is>
-          <t>Khóa ngoại — tra DIM_CLOS_PRODUCT (layer Sub Product). Khóa JOIN dùng SUB_PRODUCT_NAME (không phải SUB_PRODUCT_CODE) — NG_SB_CLOS_CUST_INFO.SUB_PRODUCT lưu giá trị TÊN sản phẩm nhánh (xác nhận SRS BC9 + người dùng), không phải mã [CẦN REVIEW] Mặc định -1 nếu không khớp</t>
-        </is>
-      </c>
-      <c r="E21" s="28" t="inlineStr">
+      <c r="D21" s="54" t="inlineStr">
+        <is>
+          <t>Khóa ngoại — tra DIM_CLOS_PRODUCT (layer Sub Product). Khóa JOIN dùng SUB_PRODUCT_NAME (không phải SUB_PRODUCT_CODE) — NG_SB_CLOS_CUST_INFO.SUB_PRODUCT lưu giá trị TÊN sản phẩm nhánh (xác nhận SRS BC9 + người dùng), không phải mã</t>
+        </is>
+      </c>
+      <c r="E21" s="31" t="inlineStr">
         <is>
           <t>F.SUB_PRODUCT_SK</t>
         </is>
       </c>
-      <c r="F21" s="28" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1">
+    </row>
+    <row r="22" ht="60" customHeight="1">
       <c r="A22" s="28" t="inlineStr">
         <is>
           <t>COMPANY_SK</t>
@@ -1073,19 +1063,18 @@
           <t>Khóa tới đơn vị kinh doanh</t>
         </is>
       </c>
-      <c r="D22" s="27" t="inlineStr">
-        <is>
-          <t>Khóa ngoại — tra DIM_LOS_COMPANY. Lookup theo layer Company (COMPANY_EFF_DATE/COMPANY_EXP_DATE), thay cho EFF_DATE/EXP_DATE chung cũ — DIM_LOS_COMPANY tách 3 layer SCD2 độc lập [CẦN REVIEW] Mặc định -1 nếu không khớp</t>
-        </is>
-      </c>
-      <c r="E22" s="28" t="inlineStr">
+      <c r="D22" s="54" t="inlineStr">
+        <is>
+          <t>Khóa ngoại — tra DIM_LOS_COMPANY. Lookup theo layer Company (COMPANY_EFF_DATE/COMPANY_EXP_DATE), thay cho EFF_DATE/EXP_DATE chung cũ — DIM_LOS_COMPANY tách 3 layer SCD2 độc lập</t>
+        </is>
+      </c>
+      <c r="E22" s="31" t="inlineStr">
         <is>
           <t>G.DIMENSION_KEY</t>
         </is>
       </c>
-      <c r="F22" s="28" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1">
+    </row>
+    <row r="23" ht="45" customHeight="1">
       <c r="A23" s="28" t="inlineStr">
         <is>
           <t>CUSTOMER_SK</t>
@@ -1101,17 +1090,16 @@
           <t>Khóa tới khách hàng</t>
         </is>
       </c>
-      <c r="D23" s="27" t="inlineStr">
-        <is>
-          <t>Khóa ngoại — tra DIM_CLOS_CUSTOMER. Đây là chân khách hàng LOS — khác T24_CUSTOMER_SK. Quan hệ N:1 (nhiều hồ sơ/DAYID của cùng khách hàng có thể trỏ cùng 1 CUSTOMER_SK) [CẦN REVIEW] Mặc định -1 nếu không khớp</t>
-        </is>
-      </c>
-      <c r="E23" s="28" t="inlineStr">
+      <c r="D23" s="54" t="inlineStr">
+        <is>
+          <t>Khóa ngoại — tra DIM_CLOS_CUSTOMER. Đây là chân khách hàng LOS — khác T24_CUSTOMER_SK. Quan hệ N:1 (nhiều hồ sơ/DAYID của cùng khách hàng có thể trỏ cùng 1 CUSTOMER_SK)</t>
+        </is>
+      </c>
+      <c r="E23" s="31" t="inlineStr">
         <is>
           <t>I.DIMENSION_KEY</t>
         </is>
       </c>
-      <c r="F23" s="28" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="28" t="inlineStr">
@@ -1129,19 +1117,18 @@
           <t>Mã hồ sơ tín dụng</t>
         </is>
       </c>
-      <c r="D24" s="27" t="inlineStr">
+      <c r="D24" s="54" t="inlineStr">
         <is>
           <t>Mã hồ sơ tín dụng CLOS</t>
         </is>
       </c>
-      <c r="E24" s="28" t="inlineStr">
+      <c r="E24" s="31" t="inlineStr">
         <is>
           <t>A.WI_NAME</t>
         </is>
       </c>
-      <c r="F24" s="28" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1">
+    </row>
+    <row r="25" ht="105" customHeight="1">
       <c r="A25" s="28" t="inlineStr">
         <is>
           <t>PROCESSED_DATE</t>
@@ -1157,17 +1144,16 @@
           <t>Ngày xử lý hồ sơ</t>
         </is>
       </c>
-      <c r="D25" s="27" t="inlineStr">
+      <c r="D25" s="54" t="inlineStr">
         <is>
           <t>Ngày xử lý chung của hồ sơ theo 3 mức ưu tiên (COALESCE theo thứ tự): (1) MAX(EXITDATE) tại bước phê duyệt đã hoàn tất; (2) NVL(EXITDATE,ENTRYDATE) tại WORKSTEP='CancelRevoke'; (3) EXITDATE của sự kiện hoàn tất gần nhất</t>
         </is>
       </c>
-      <c r="E25" s="28" t="inlineStr">
+      <c r="E25" s="31" t="inlineStr">
         <is>
           <t>COALESCE((SELECT MAX(C.EXITDATE) FROM C WHERE C.WINAME = A.WI_NAME AND C.WORKSTEP IN ('CreditCommittee','CreditApproval') AND C.DECISION IN ('Send To HOSupport','Reject','Submit','Send To PostSanction','Submit To DisbursementMaker')), (SELECT NVL(C.EXITDATE, C.ENTRYDATE) FROM C WHERE C.WINAME = A.WI_NAME AND C.WORKSTEP = 'CancelRevoke'), (SELECT C.EXITDATE FROM C WHERE C.WINAME = A.WI_NAME AND C.EXITDATE IS NOT NULL ORDER BY C.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY))</t>
         </is>
       </c>
-      <c r="F25" s="28" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="28" t="inlineStr">
@@ -1185,17 +1171,16 @@
           <t>Số tiền đề xuất</t>
         </is>
       </c>
-      <c r="D26" s="27" t="inlineStr">
+      <c r="D26" s="54" t="inlineStr">
         <is>
           <t>Số tiền đề xuất</t>
         </is>
       </c>
-      <c r="E26" s="28" t="inlineStr">
+      <c r="E26" s="31" t="inlineStr">
         <is>
           <t>J.PRECREDITLIMIT</t>
         </is>
       </c>
-      <c r="F26" s="28" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="28" t="inlineStr">
@@ -1213,19 +1198,18 @@
           <t>Hạn mức chuyên gia phê duyệt</t>
         </is>
       </c>
-      <c r="D27" s="27" t="inlineStr">
+      <c r="D27" s="54" t="inlineStr">
         <is>
           <t>Hạn mức do chuyên gia phê duyệt</t>
         </is>
       </c>
-      <c r="E27" s="28" t="inlineStr">
+      <c r="E27" s="31" t="inlineStr">
         <is>
           <t>K.CREDIT_LIMIT</t>
         </is>
       </c>
-      <c r="F27" s="28" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1">
+    </row>
+    <row r="28" ht="30" customHeight="1">
       <c r="A28" s="28" t="inlineStr">
         <is>
           <t>APPROVED_AMT_FINAL</t>
@@ -1241,17 +1225,16 @@
           <t>Hạn mức phê duyệt cuối cùng</t>
         </is>
       </c>
-      <c r="D28" s="27" t="inlineStr">
+      <c r="D28" s="54" t="inlineStr">
         <is>
           <t>Hạn mức phê duyệt cuối cùng (BC1.LOAN_AMOUNT, BC3.CREDIT_LIMIT)</t>
         </is>
       </c>
-      <c r="E28" s="28" t="inlineStr">
+      <c r="E28" s="31" t="inlineStr">
         <is>
           <t>J.CREDIT_LIMIT</t>
         </is>
       </c>
-      <c r="F28" s="28" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="28" t="inlineStr">
@@ -1269,19 +1252,18 @@
           <t>Kỳ hạn phê duyệt</t>
         </is>
       </c>
-      <c r="D29" s="27" t="inlineStr">
+      <c r="D29" s="54" t="inlineStr">
         <is>
           <t>Kỳ hạn phê duyệt, giữ nguyên văn gốc vì có giá trị không ép được sang số</t>
         </is>
       </c>
-      <c r="E29" s="28" t="inlineStr">
+      <c r="E29" s="31" t="inlineStr">
         <is>
           <t>J.CREDIT_TERM</t>
         </is>
       </c>
-      <c r="F29" s="28" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1">
+    </row>
+    <row r="30" ht="30" customHeight="1">
       <c r="A30" s="28" t="inlineStr">
         <is>
           <t>INTEREST_RATE_PCT</t>
@@ -1297,17 +1279,16 @@
           <t>Lãi suất phê duyệt</t>
         </is>
       </c>
-      <c r="D30" s="27" t="inlineStr">
+      <c r="D30" s="54" t="inlineStr">
         <is>
           <t>Lãi suất phê duyệt (%), giữ nguyên văn gốc vì có giá trị không ép được sang số (ví dụ 'Theo thỏa thuận')</t>
         </is>
       </c>
-      <c r="E30" s="28" t="inlineStr">
+      <c r="E30" s="31" t="inlineStr">
         <is>
           <t>J.INTEREST_RATE</t>
         </is>
       </c>
-      <c r="F30" s="28" t="n"/>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" s="28" t="inlineStr">
@@ -1325,19 +1306,18 @@
           <t>Loại tiền</t>
         </is>
       </c>
-      <c r="D31" s="27" t="inlineStr">
+      <c r="D31" s="54" t="inlineStr">
         <is>
           <t>Loại tiền</t>
         </is>
       </c>
-      <c r="E31" s="28" t="inlineStr">
+      <c r="E31" s="31" t="inlineStr">
         <is>
           <t>J.CURRENCY</t>
         </is>
       </c>
-      <c r="F31" s="28" t="n"/>
-    </row>
-    <row r="32" ht="15" customHeight="1">
+    </row>
+    <row r="32" ht="75" customHeight="1">
       <c r="A32" s="28" t="inlineStr">
         <is>
           <t>APPLICATION_LINK_INFO</t>
@@ -1353,19 +1333,18 @@
           <t>Thông tin liên kết hồ sơ</t>
         </is>
       </c>
-      <c r="D32" s="27" t="inlineStr">
-        <is>
-          <t>Thông tin liên kết hồ sơ — cột generic của WFINSTRUMENTTABLE — đổi tên từ VAR_STR12 (review 2026-10-04, theo yêu cầu người dùng). LEFT JOIN riêng theo WI_NAME=PROCESSINSTANCEID (không lọc CREATEDBY). Dùng làm điều kiện lọc IS NOT NULL cho SLHS_CLOS/SLGN_CLOS (AGG_LOS_KPI_YTD_DAILY)</t>
-        </is>
-      </c>
-      <c r="E32" s="28" t="inlineStr">
+      <c r="D32" s="54" t="inlineStr">
+        <is>
+          <t>Thông tin liên kết hồ sơ — cột generic của WFINSTRUMENTTABLE — đổi tên từ VAR_STR12. LEFT JOIN riêng theo WI_NAME=PROCESSINSTANCEID (không lọc CREATEDBY). Dùng làm điều kiện lọc IS NOT NULL cho SLHS_CLOS/SLGN_CLOS (AGG_LOS_KPI_YTD_DAILY)</t>
+        </is>
+      </c>
+      <c r="E32" s="31" t="inlineStr">
         <is>
           <t>L.VAR_STR12</t>
         </is>
       </c>
-      <c r="F32" s="28" t="n"/>
-    </row>
-    <row r="33" ht="15" customHeight="1">
+    </row>
+    <row r="33" ht="30" customHeight="1">
       <c r="A33" s="28" t="inlineStr">
         <is>
           <t>LG_REQ</t>
@@ -1381,17 +1360,16 @@
           <t>Cờ yêu cầu bảo lãnh</t>
         </is>
       </c>
-      <c r="D33" s="27" t="inlineStr">
+      <c r="D33" s="54" t="inlineStr">
         <is>
           <t>Cờ yêu cầu bảo lãnh (Letter of Guarantee) phát sinh theo hồ sơ (boolean true/false). Thiết kế dư thừa</t>
         </is>
       </c>
-      <c r="E33" s="28" t="inlineStr">
+      <c r="E33" s="31" t="inlineStr">
         <is>
           <t>E.LG_REQ</t>
         </is>
       </c>
-      <c r="F33" s="28" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" s="28" t="inlineStr">
@@ -1409,17 +1387,16 @@
           <t>Cờ yêu cầu FI</t>
         </is>
       </c>
-      <c r="D34" s="27" t="inlineStr">
+      <c r="D34" s="54" t="inlineStr">
         <is>
           <t>Cờ yêu cầu (boolean true/false). Thiết kế dư thừa</t>
         </is>
       </c>
-      <c r="E34" s="28" t="inlineStr">
+      <c r="E34" s="31" t="inlineStr">
         <is>
           <t>E.FI_REQ</t>
         </is>
       </c>
-      <c r="F34" s="28" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" s="28" t="inlineStr">
@@ -1437,19 +1414,18 @@
           <t>Cờ yêu cầu xác minh ĐT</t>
         </is>
       </c>
-      <c r="D35" s="27" t="inlineStr">
+      <c r="D35" s="54" t="inlineStr">
         <is>
           <t>Cờ yêu cầu xác minh điện thoại (boolean true/false). Thiết kế dư thừa</t>
         </is>
       </c>
-      <c r="E35" s="28" t="inlineStr">
+      <c r="E35" s="31" t="inlineStr">
         <is>
           <t>E.PHONE_REQ</t>
         </is>
       </c>
-      <c r="F35" s="28" t="n"/>
-    </row>
-    <row r="36" ht="15" customHeight="1">
+    </row>
+    <row r="36" ht="75" customHeight="1">
       <c r="A36" s="28" t="inlineStr">
         <is>
           <t>CHANGE_REQUEST</t>
@@ -1465,19 +1441,18 @@
           <t>Yêu cầu điều chỉnh hồ sơ</t>
         </is>
       </c>
-      <c r="D36" s="27" t="inlineStr">
+      <c r="D36" s="54" t="inlineStr">
         <is>
           <t>Yêu cầu điều chỉnh hồ sơ — nguồn NG_SB_CLOS_CHANGEREQ.CHANGE_REQUEST. Chuyển từ DIM_CLOS_APPLICATION sang đây (đối chiếu SRS BC2) — bản chất thay đổi thường xuyên theo hồ sơ, không phù hợp cột ổn định SCD2 của DIM, giống cách RLOS đã làm</t>
         </is>
       </c>
-      <c r="E36" s="28" t="inlineStr">
+      <c r="E36" s="31" t="inlineStr">
         <is>
           <t>M.CHANGE_REQUEST</t>
         </is>
       </c>
-      <c r="F36" s="28" t="n"/>
-    </row>
-    <row r="37" ht="15" customHeight="1">
+    </row>
+    <row r="37" ht="75" customHeight="1">
       <c r="A37" s="28" t="inlineStr">
         <is>
           <t>CHANGE_TYPE</t>
@@ -1493,291 +1468,171 @@
           <t>Loại thay đổi điều kiện phê duyệt</t>
         </is>
       </c>
-      <c r="D37" s="27" t="inlineStr">
+      <c r="D37" s="54" t="inlineStr">
         <is>
           <t>Loại thay đổi điều kiện phê duyệt, giữ nguyên chuỗi gốc kể cả dạng đa giá trị nối bằng dấu '~' — nguồn NG_SB_CLOS_CHANGEREQ.CHANGE_TYPE, giữ nguyên văn không qua bảng danh mục nào (khác RLOS có DIM_RLOS_CHANGE_TYPE)</t>
         </is>
       </c>
-      <c r="E37" s="28" t="inlineStr">
+      <c r="E37" s="31" t="inlineStr">
         <is>
           <t>M.CHANGE_TYPE</t>
         </is>
       </c>
-      <c r="F37" s="28" t="n"/>
-    </row>
-    <row r="38" ht="51" customHeight="1"/>
+    </row>
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="10" t="n"/>
       <c r="B39" s="10" t="n"/>
       <c r="C39" s="10" t="n"/>
-      <c r="D39" s="54" t="inlineStr">
+      <c r="D39" s="55" t="inlineStr">
         <is>
           <t>Điều kiện join giữa các bảng</t>
         </is>
       </c>
       <c r="E39" s="10" t="n"/>
-      <c r="F39" s="10" t="n"/>
-    </row>
-    <row r="40" ht="45" customHeight="1">
+    </row>
+    <row r="40" ht="30" customHeight="1">
       <c r="A40" s="25" t="n"/>
       <c r="B40" s="25" t="n"/>
       <c r="C40" s="51" t="n"/>
-      <c r="D40" s="8" t="n"/>
+      <c r="D40" s="54" t="n"/>
       <c r="E40" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN B.WI_NAME = A.WI_NAME AND v_batch_date BETWEEN B.EFF_DATE AND NVL(B.EXP_DATE, v_batch_date)</t>
         </is>
       </c>
-      <c r="F40" s="8" t="n"/>
-    </row>
-    <row r="41" ht="75" customHeight="1">
+    </row>
+    <row r="41" ht="45" customHeight="1">
       <c r="A41" s="25" t="n"/>
       <c r="B41" s="25" t="n"/>
       <c r="C41" s="51" t="n"/>
-      <c r="D41" s="8" t="n"/>
+      <c r="D41" s="54" t="n"/>
       <c r="E41" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN (SELECT C.WORKSTEP, C.DECISION FROM C WHERE C.WINAME = A.WI_NAME AND C.EXITDATE IS NOT NULL AND C.ENTRYDATE &lt;= v_batch_date ORDER BY C.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY) LAST_EVENT ON 1=1</t>
         </is>
       </c>
-      <c r="F41" s="8" t="n"/>
-    </row>
-    <row r="42" ht="60" customHeight="1">
+    </row>
+    <row r="42" ht="45" customHeight="1">
       <c r="A42" s="25" t="n"/>
       <c r="B42" s="25" t="n"/>
       <c r="C42" s="51" t="n"/>
-      <c r="D42" s="8" t="n"/>
+      <c r="D42" s="54" t="n"/>
       <c r="E42" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN D.WORKSTEP_CODE = LAST_EVENT.WORKSTEP AND D.DECISION_CODE = LAST_EVENT.DECISION AND v_batch_date BETWEEN D.EFF_DATE AND NVL(D.EXP_DATE, v_batch_date)</t>
         </is>
       </c>
-      <c r="F42" s="8" t="n"/>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" s="25" t="n"/>
       <c r="B43" s="25" t="n"/>
       <c r="C43" s="51" t="n"/>
-      <c r="D43" s="8" t="n"/>
+      <c r="D43" s="54" t="n"/>
       <c r="E43" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN E.WI_NAME = A.WI_NAME</t>
         </is>
       </c>
-      <c r="F43" s="8" t="n"/>
-    </row>
-    <row r="44" ht="60" customHeight="1">
+    </row>
+    <row r="44" ht="30" customHeight="1">
       <c r="A44" s="25" t="n"/>
       <c r="B44" s="25" t="n"/>
       <c r="C44" s="51" t="n"/>
-      <c r="D44" s="8" t="n"/>
+      <c r="D44" s="54" t="n"/>
       <c r="E44" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN F.PRODUCTLINE_CODE = E.PRODUCT_LINE AND v_batch_date BETWEEN F.PRODUCTLINE_EFF_DATE AND NVL(F.PRODUCTLINE_EXP_DATE, v_batch_date)</t>
         </is>
       </c>
-      <c r="F44" s="8" t="n"/>
-    </row>
-    <row r="45" ht="60" customHeight="1">
+    </row>
+    <row r="45" ht="30" customHeight="1">
       <c r="A45" s="25" t="n"/>
       <c r="B45" s="25" t="n"/>
       <c r="C45" s="51" t="n"/>
-      <c r="D45" s="8" t="n"/>
+      <c r="D45" s="54" t="n"/>
       <c r="E45" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN F.SUB_PRODUCT_NAME = E.SUB_PRODUCT AND v_batch_date BETWEEN F.SUB_PRODUCT_EFF_DATE AND NVL(F.SUB_PRODUCT_EXP_DATE, v_batch_date)</t>
         </is>
       </c>
-      <c r="F45" s="8" t="n"/>
-    </row>
-    <row r="46" ht="45" customHeight="1">
+    </row>
+    <row r="46" ht="30" customHeight="1">
       <c r="A46" s="25" t="n"/>
       <c r="B46" s="25" t="n"/>
       <c r="C46" s="51" t="n"/>
-      <c r="D46" s="8" t="n"/>
+      <c r="D46" s="54" t="n"/>
       <c r="E46" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN G.COMPANY_CODE = E.COMPANY_CODE AND v_batch_date BETWEEN G.COMPANY_EFF_DATE AND NVL(G.COMPANY_EXP_DATE, v_batch_date)</t>
         </is>
       </c>
-      <c r="F46" s="8" t="n"/>
-    </row>
-    <row r="47" ht="60" customHeight="1">
+    </row>
+    <row r="47" ht="45" customHeight="1">
       <c r="A47" s="25" t="n"/>
       <c r="B47" s="25" t="n"/>
       <c r="C47" s="51" t="n"/>
-      <c r="D47" s="8" t="n"/>
+      <c r="D47" s="54" t="n"/>
       <c r="E47" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN H.WI_NAME = A.WI_NAME AND UPPER(H.OBJ_TYPE) = 'KHÁCH HÀNG' AND ROW_NUMBER() OVER (PARTITION BY H.WI_NAME ORDER BY H.RECID DESC) = 1</t>
         </is>
       </c>
-      <c r="F47" s="8" t="n"/>
-    </row>
-    <row r="48" ht="45" customHeight="1">
+    </row>
+    <row r="48" ht="30" customHeight="1">
       <c r="A48" s="25" t="n"/>
       <c r="B48" s="25" t="n"/>
       <c r="C48" s="51" t="n"/>
-      <c r="D48" s="8" t="n"/>
+      <c r="D48" s="54" t="n"/>
       <c r="E48" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN I.CUSTOMER_CODE = H.ID_NUMBER AND v_batch_date BETWEEN I.EFF_DATE AND NVL(I.EXP_DATE, v_batch_date)</t>
         </is>
       </c>
-      <c r="F48" s="8" t="n"/>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" s="25" t="n"/>
       <c r="B49" s="25" t="n"/>
       <c r="C49" s="51" t="n"/>
-      <c r="D49" s="8" t="n"/>
+      <c r="D49" s="54" t="n"/>
       <c r="E49" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN J.WI_NAME = A.WI_NAME</t>
         </is>
       </c>
-      <c r="F49" s="8" t="n"/>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" s="25" t="n"/>
       <c r="B50" s="25" t="n"/>
       <c r="C50" s="51" t="n"/>
-      <c r="D50" s="8" t="n"/>
+      <c r="D50" s="54" t="n"/>
       <c r="E50" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN K.WI_NAME = A.WI_NAME</t>
         </is>
       </c>
-      <c r="F50" s="8" t="n"/>
-    </row>
-    <row r="51" ht="60" customHeight="1">
+    </row>
+    <row r="51" ht="30" customHeight="1">
       <c r="A51" s="25" t="n"/>
       <c r="B51" s="25" t="n"/>
       <c r="C51" s="51" t="n"/>
-      <c r="D51" s="8" t="n"/>
+      <c r="D51" s="54" t="n"/>
       <c r="E51" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN L.PROCESSINSTANCEID = A.WI_NAME AND ROW_NUMBER() OVER (PARTITION BY L.PROCESSINSTANCEID ORDER BY L.CREATEDBY) = 1</t>
         </is>
       </c>
-      <c r="F51" s="8" t="n"/>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" s="25" t="n"/>
       <c r="B52" s="25" t="n"/>
       <c r="C52" s="51" t="n"/>
-      <c r="D52" s="8" t="n"/>
+      <c r="D52" s="54" t="n"/>
       <c r="E52" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN M.WI_NAME = A.WI_NAME</t>
         </is>
       </c>
-      <c r="F52" s="8" t="n"/>
-    </row>
-    <row r="53" ht="34" customHeight="1"/>
-    <row r="54" ht="34" customHeight="1"/>
-    <row r="55" ht="34" customHeight="1"/>
-    <row r="56" ht="68" customHeight="1"/>
-    <row r="57" ht="51" customHeight="1"/>
-    <row r="58" ht="34" customHeight="1"/>
-    <row r="59" ht="17" customHeight="1"/>
-    <row r="60" ht="34" customHeight="1"/>
-    <row r="61" ht="17" customHeight="1"/>
-    <row r="62" ht="85" customHeight="1"/>
-    <row r="63" ht="85" customHeight="1"/>
-    <row r="64" ht="34" customHeight="1"/>
-    <row r="65" ht="17" customHeight="1"/>
-    <row r="66" ht="34" customHeight="1"/>
-    <row r="67" ht="51" customHeight="1"/>
-    <row r="68" ht="51" customHeight="1"/>
-    <row r="69" ht="51" customHeight="1"/>
-    <row r="70" ht="17" customHeight="1"/>
-    <row r="71" ht="34" customHeight="1"/>
-    <row r="72" ht="34" customHeight="1"/>
-    <row r="73" ht="34" customHeight="1"/>
-    <row r="74" ht="34" customHeight="1"/>
-    <row r="75" ht="34" customHeight="1"/>
-    <row r="76" ht="34" customHeight="1"/>
-    <row r="77" ht="51" customHeight="1"/>
-    <row r="78" ht="34" customHeight="1"/>
-    <row r="79" ht="51" customHeight="1"/>
-    <row r="80" ht="17" customHeight="1"/>
-    <row r="81" ht="17" customHeight="1"/>
-    <row r="82" ht="17" customHeight="1"/>
-    <row r="83" ht="17" customHeight="1"/>
-    <row r="84" ht="17" customHeight="1"/>
-    <row r="85" ht="17" customHeight="1"/>
-    <row r="86" ht="17" customHeight="1"/>
-    <row r="87" ht="17" customHeight="1"/>
-    <row r="88" ht="17" customHeight="1"/>
-    <row r="89" ht="17" customHeight="1"/>
-    <row r="90" ht="34" customHeight="1"/>
-    <row r="91" ht="17" customHeight="1"/>
-    <row r="92" ht="17" customHeight="1"/>
-    <row r="93" ht="17" customHeight="1"/>
-    <row r="94" ht="17" customHeight="1"/>
-    <row r="95" ht="17" customHeight="1"/>
-    <row r="96" ht="17" customHeight="1"/>
-    <row r="97" ht="17" customHeight="1"/>
-    <row r="100" ht="187" customHeight="1"/>
-    <row r="101" ht="17" customHeight="1"/>
-    <row r="102" ht="17" customHeight="1"/>
-    <row r="103" ht="17" customHeight="1"/>
-    <row r="104" ht="17" customHeight="1"/>
-    <row r="105" ht="17" customHeight="1"/>
-    <row r="106" ht="17" customHeight="1"/>
-    <row r="107" ht="17" customHeight="1"/>
-    <row r="108" ht="17" customHeight="1"/>
-    <row r="109" ht="17" customHeight="1"/>
-    <row r="110" ht="17" customHeight="1"/>
-    <row r="111" ht="17" customHeight="1"/>
-    <row r="112" ht="17" customHeight="1"/>
-    <row r="113" ht="17" customHeight="1"/>
-    <row r="114" ht="17" customHeight="1"/>
-    <row r="115" ht="17" customHeight="1"/>
-    <row r="116" ht="17" customHeight="1"/>
-    <row r="117" ht="17" customHeight="1"/>
-    <row r="118" ht="17" customHeight="1"/>
-    <row r="119" ht="17" customHeight="1"/>
-    <row r="120" ht="68" customHeight="1"/>
-    <row r="121" ht="51" customHeight="1"/>
-    <row r="122" ht="34" customHeight="1"/>
-    <row r="123" ht="153" customHeight="1"/>
-    <row r="124" ht="17" customHeight="1"/>
-    <row r="125" ht="17" customHeight="1"/>
-    <row r="132" ht="60" customHeight="1"/>
-    <row r="133" ht="17" customHeight="1"/>
-    <row r="134" ht="17" customHeight="1"/>
-    <row r="135" ht="17" customHeight="1"/>
-    <row r="136" ht="17" customHeight="1"/>
-    <row r="137" ht="51" customHeight="1"/>
-    <row r="138" ht="45" customHeight="1"/>
-    <row r="139" ht="120" customHeight="1"/>
-    <row r="141" ht="384" customHeight="1"/>
-    <row r="143" ht="34" customHeight="1"/>
-    <row r="148" ht="119" customHeight="1"/>
-    <row r="149" ht="17" customHeight="1"/>
-    <row r="150" ht="17" customHeight="1"/>
-    <row r="151" ht="17" customHeight="1"/>
-    <row r="152" ht="51" customHeight="1"/>
-    <row r="153" ht="34" customHeight="1"/>
-    <row r="154" ht="30" customHeight="1"/>
-    <row r="155" ht="17" customHeight="1"/>
-    <row r="157" ht="119" customHeight="1"/>
-    <row r="158" ht="17" customHeight="1"/>
-    <row r="159" ht="17" customHeight="1"/>
-    <row r="160" ht="17" customHeight="1"/>
-    <row r="161" ht="17" customHeight="1"/>
-    <row r="162" ht="17" customHeight="1"/>
-    <row r="163" ht="17" customHeight="1"/>
-    <row r="164" ht="17" customHeight="1"/>
-    <row r="165" ht="17" customHeight="1"/>
-    <row r="166" ht="34" customHeight="1"/>
-    <row r="167" ht="34" customHeight="1"/>
-    <row r="168" ht="16" customHeight="1"/>
-    <row r="169" ht="17" customHeight="1"/>
-    <row r="170" ht="17" customHeight="1"/>
-    <row r="2480" customFormat="1" s="19"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/mapping/SB_DWH/Mapping_FCT_CLOS_APPLICATION.xlsx
+++ b/mapping/SB_DWH/Mapping_FCT_CLOS_APPLICATION.xlsx
@@ -718,7 +718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16"/>
   <cols>
     <col width="34.33203125" customWidth="1" style="19" min="1" max="1"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="B2" s="19" t="inlineStr">
         <is>
-          <t>Bảng Fact snapshot hồ sơ tín dụng CLOS theo ngày, driving từ NG_SB_CLOS_EXTTABLE</t>
+          <t>Bảng FACT xương sống của CLOS tại SB_DWH — ảnh trạng thái cuối ngày của từng hồ sơ tín dụng doanh nghiệp (CLOS)</t>
         </is>
       </c>
       <c r="E2" s="52" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="E3" s="52" t="inlineStr">
         <is>
-          <t>NG_SB_CLOS_ENTRY_EXIT AS C</t>
+          <t>DIM_CLOS_WORKSTEP_DECISION AS C</t>
         </is>
       </c>
     </row>
@@ -794,7 +794,7 @@
       </c>
       <c r="E4" s="52" t="inlineStr">
         <is>
-          <t>DIM_CLOS_WORKSTEP_DECISION AS D</t>
+          <t>NG_SB_CLOS_ENTRY_EXIT AS D</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       <c r="A5" s="13" t="n"/>
       <c r="E5" s="52" t="inlineStr">
         <is>
-          <t>NG_SB_CLOS_CUST_INFO AS E</t>
+          <t>DIM_CLOS_PRODUCT AS E</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       <c r="A6" s="13" t="n"/>
       <c r="E6" s="52" t="inlineStr">
         <is>
-          <t>DIM_CLOS_PRODUCT AS F</t>
+          <t>NG_SB_CLOS_CUST_INFO AS F</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       <c r="A8" s="13" t="n"/>
       <c r="E8" s="52" t="inlineStr">
         <is>
-          <t>NG_SB_CLOS_CUST_INFO_LEGAL AS H</t>
+          <t>DIM_CLOS_CUSTOMER AS H</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       <c r="A9" s="13" t="n"/>
       <c r="E9" s="53" t="inlineStr">
         <is>
-          <t>DIM_CLOS_CUSTOMER AS I</t>
+          <t>NG_SB_CLOS_CUST_INFO_LEGAL AS I</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
       </c>
       <c r="E16" s="6" t="n"/>
     </row>
-    <row r="17" ht="45" customHeight="1">
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="28" t="inlineStr">
         <is>
           <t>DAYID</t>
@@ -930,7 +930,7 @@
       </c>
       <c r="D17" s="54" t="inlineStr">
         <is>
-          <t>PK — Driving: NG_SB_CLOS_EXTTABLE. Ngày dữ liệu, dạng số YYYYMMDD. Full snapshot: mọi WI_NAME còn hiệu lực trên EXTTABLE sinh dòng ở MỌI DAYID</t>
+          <t>Ngày dữ liệu, dạng số YYYYMMDD. Full snapshot: mọi WI_NAME còn hiệu lực trên EXTTABLE sinh dòng ở MỌI DAYID.</t>
         </is>
       </c>
       <c r="E17" s="31" t="inlineStr">
@@ -939,7 +939,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
+    <row r="18" ht="30" customHeight="1">
       <c r="A18" s="28" t="inlineStr">
         <is>
           <t>APPLICATION_SK</t>
@@ -952,12 +952,12 @@
       </c>
       <c r="C18" s="26" t="inlineStr">
         <is>
-          <t>Khóa tới hồ sơ tín dụng</t>
+          <t>Khóa hồ sơ tín dụng</t>
         </is>
       </c>
       <c r="D18" s="54" t="inlineStr">
         <is>
-          <t>Khóa ngoại — tra DIM_CLOS_APPLICATION</t>
+          <t>Khóa ngoại — tra DIM_CLOS_APPLICATION. Mặc định -1 nếu không khớp</t>
         </is>
       </c>
       <c r="E18" s="31" t="inlineStr">
@@ -966,118 +966,118 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="75" customHeight="1">
+    <row r="19" ht="15" customHeight="1">
       <c r="A19" s="28" t="inlineStr">
         <is>
+          <t>WI_NAME</t>
+        </is>
+      </c>
+      <c r="B19" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(100)</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="inlineStr">
+        <is>
+          <t>Mã hồ sơ tín dụng</t>
+        </is>
+      </c>
+      <c r="D19" s="54" t="inlineStr">
+        <is>
+          <t>Mã hồ sơ tín dụng CLOS</t>
+        </is>
+      </c>
+      <c r="E19" s="31" t="inlineStr">
+        <is>
+          <t>A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="75" customHeight="1">
+      <c r="A20" s="28" t="inlineStr">
+        <is>
           <t>WORKSTEP_DECISION_SK</t>
         </is>
       </c>
-      <c r="B19" s="25" t="inlineStr">
+      <c r="B20" s="25" t="inlineStr">
         <is>
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="C19" s="26" t="inlineStr">
-        <is>
-          <t>Khóa tới bước/quyết định gần nhất</t>
-        </is>
-      </c>
-      <c r="D19" s="54" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_CLOS_WORKSTEP_DECISION (gộp từ LAST_WORKSTEP_SK+LAST_DECISION_SK) của sự kiện hoàn tất gần nhất — đổi tên từ LAST_WORKSTEP_DECISION_SK. Lookup theo cặp WORKSTEP_CODE+DECISION_CODE của sự kiện hoàn tất gần nhất</t>
-        </is>
-      </c>
-      <c r="E19" s="31" t="inlineStr">
-        <is>
-          <t>D.DIMENSION_KEY</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="45" customHeight="1">
-      <c r="A20" s="28" t="inlineStr">
-        <is>
-          <t>PRODUCTLINE_SK</t>
-        </is>
-      </c>
-      <c r="B20" s="25" t="inlineStr">
-        <is>
-          <t>NUMBER</t>
-        </is>
-      </c>
       <c r="C20" s="26" t="inlineStr">
         <is>
-          <t>Khóa layer Product Line</t>
+          <t>Khóa bước &amp; quyết định cuối</t>
         </is>
       </c>
       <c r="D20" s="54" t="inlineStr">
         <is>
-          <t>Khóa ngoại — tra DIM_CLOS_PRODUCT (layer Product Line). Thay cho PRODUCT_SK cũ — DIM_CLOS_PRODUCT tách 2 layer SCD2 độc lập (Product Line/Sub Product)</t>
+          <t>Khóa tới DIM_CLOS_WORKSTEP_DECISION (gộp từ LAST_WORKSTEP_SK+LAST_DECISION_SK) của sự kiện hoàn tất gần nhất — đổi tên từ LAST_WORKSTEP_DECISION_SK. Lookup theo cặp WORKSTEP_CODE+DECISION_CODE của sự kiện hoàn tất gần nhất. Mặc định -1</t>
         </is>
       </c>
       <c r="E20" s="31" t="inlineStr">
         <is>
-          <t>F.PRODUCTLINE_SK</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="75" customHeight="1">
+          <t>C.DIMENSION_KEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="45" customHeight="1">
       <c r="A21" s="28" t="inlineStr">
         <is>
-          <t>SUB_PRODUCT_SK</t>
+          <t>WORKSTEP_CODE</t>
         </is>
       </c>
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>VARCHAR2(200)</t>
         </is>
       </c>
       <c r="C21" s="26" t="inlineStr">
         <is>
-          <t>Khóa layer Sub Product</t>
+          <t>Mã bước xử lý cuối</t>
         </is>
       </c>
       <c r="D21" s="54" t="inlineStr">
         <is>
-          <t>Khóa ngoại — tra DIM_CLOS_PRODUCT (layer Sub Product). Khóa JOIN dùng SUB_PRODUCT_NAME (không phải SUB_PRODUCT_CODE) — NG_SB_CLOS_CUST_INFO.SUB_PRODUCT lưu giá trị TÊN sản phẩm nhánh (xác nhận SRS BC9 + người dùng), không phải mã</t>
+          <t>CỘT MỚI — BK cạnh SK: Mã bước xử lý của sự kiện hoàn tất gần nhất, 1 phần BK composite của DIM_CLOS_WORKSTEP_DECISION (WORKSTEP_CODE+DECISION_CODE)</t>
         </is>
       </c>
       <c r="E21" s="31" t="inlineStr">
         <is>
-          <t>F.SUB_PRODUCT_SK</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="60" customHeight="1">
+          <t>LAST_EVENT.WORKSTEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
       <c r="A22" s="28" t="inlineStr">
         <is>
-          <t>COMPANY_SK</t>
+          <t>DECISION_CODE</t>
         </is>
       </c>
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>VARCHAR2(200)</t>
         </is>
       </c>
       <c r="C22" s="26" t="inlineStr">
         <is>
-          <t>Khóa tới đơn vị kinh doanh</t>
+          <t>Mã quyết định cuối</t>
         </is>
       </c>
       <c r="D22" s="54" t="inlineStr">
         <is>
-          <t>Khóa ngoại — tra DIM_LOS_COMPANY. Lookup theo layer Company (COMPANY_EFF_DATE/COMPANY_EXP_DATE), thay cho EFF_DATE/EXP_DATE chung cũ — DIM_LOS_COMPANY tách 3 layer SCD2 độc lập</t>
+          <t>CỘT MỚI — BK cạnh SK: Mã quyết định của sự kiện hoàn tất gần nhất, nửa còn lại BK composite của DIM_CLOS_WORKSTEP_DECISION</t>
         </is>
       </c>
       <c r="E22" s="31" t="inlineStr">
         <is>
-          <t>G.DIMENSION_KEY</t>
+          <t>LAST_EVENT.DECISION</t>
         </is>
       </c>
     </row>
     <row r="23" ht="45" customHeight="1">
       <c r="A23" s="28" t="inlineStr">
         <is>
-          <t>CUSTOMER_SK</t>
+          <t>PRODUCTLINE_SK</t>
         </is>
       </c>
       <c r="B23" s="25" t="inlineStr">
@@ -1087,24 +1087,24 @@
       </c>
       <c r="C23" s="26" t="inlineStr">
         <is>
-          <t>Khóa tới khách hàng</t>
+          <t>Khóa dòng sản phẩm</t>
         </is>
       </c>
       <c r="D23" s="54" t="inlineStr">
         <is>
-          <t>Khóa ngoại — tra DIM_CLOS_CUSTOMER. Đây là chân khách hàng LOS — khác T24_CUSTOMER_SK. Quan hệ N:1 (nhiều hồ sơ/DAYID của cùng khách hàng có thể trỏ cùng 1 CUSTOMER_SK)</t>
+          <t>Khóa ngoại — tra DIM_CLOS_PRODUCT (layer Product Line). Thay cho PRODUCT_SK cũ — DIM_CLOS_PRODUCT tách 2 layer SCD2 độc lập (Product Line/Sub Product). Mặc định -1 nếu không khớp.</t>
         </is>
       </c>
       <c r="E23" s="31" t="inlineStr">
         <is>
-          <t>I.DIMENSION_KEY</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
+          <t>E.PRODUCTLINE_SK</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
       <c r="A24" s="28" t="inlineStr">
         <is>
-          <t>WI_NAME</t>
+          <t>PRODUCTLINE_CODE</t>
         </is>
       </c>
       <c r="B24" s="25" t="inlineStr">
@@ -1114,447 +1114,543 @@
       </c>
       <c r="C24" s="26" t="inlineStr">
         <is>
-          <t>Mã hồ sơ tín dụng</t>
+          <t>Mã dòng sản phẩm</t>
         </is>
       </c>
       <c r="D24" s="54" t="inlineStr">
         <is>
-          <t>Mã hồ sơ tín dụng CLOS</t>
+          <t>CỘT MỚI — BK cạnh SK: Mã dòng sản phẩm (BK của DIM_CLOS_PRODUCT layer Product Line)</t>
         </is>
       </c>
       <c r="E24" s="31" t="inlineStr">
         <is>
-          <t>A.WI_NAME</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="105" customHeight="1">
+          <t>F.PRODUCT_LINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="60" customHeight="1">
       <c r="A25" s="28" t="inlineStr">
         <is>
-          <t>PROCESSED_DATE</t>
+          <t>SUB_PRODUCT_SK</t>
         </is>
       </c>
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="C25" s="26" t="inlineStr">
         <is>
-          <t>Ngày xử lý hồ sơ</t>
+          <t>Khóa sản phẩm nhánh</t>
         </is>
       </c>
       <c r="D25" s="54" t="inlineStr">
         <is>
-          <t>Ngày xử lý chung của hồ sơ theo 3 mức ưu tiên (COALESCE theo thứ tự): (1) MAX(EXITDATE) tại bước phê duyệt đã hoàn tất; (2) NVL(EXITDATE,ENTRYDATE) tại WORKSTEP='CancelRevoke'; (3) EXITDATE của sự kiện hoàn tất gần nhất</t>
+          <t>Khóa ngoại — tra DIM_CLOS_PRODUCT (layer Sub Product). Mặc định -1 nếu không khớp. Khóa JOIN dùng SUB_PRODUCT_NAME (không phải SUB_PRODUCT_CODE) — F.SUB_PRODUCT lưu giá trị TÊN sản phẩm nhánh (xác nhận SRS BC9 + người dùng), không phải mã.</t>
         </is>
       </c>
       <c r="E25" s="31" t="inlineStr">
         <is>
-          <t>COALESCE((SELECT MAX(C.EXITDATE) FROM C WHERE C.WINAME = A.WI_NAME AND C.WORKSTEP IN ('CreditCommittee','CreditApproval') AND C.DECISION IN ('Send To HOSupport','Reject','Submit','Send To PostSanction','Submit To DisbursementMaker')), (SELECT NVL(C.EXITDATE, C.ENTRYDATE) FROM C WHERE C.WINAME = A.WI_NAME AND C.WORKSTEP = 'CancelRevoke'), (SELECT C.EXITDATE FROM C WHERE C.WINAME = A.WI_NAME AND C.EXITDATE IS NOT NULL ORDER BY C.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY))</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
+          <t>E.SUB_PRODUCT_SK</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="45" customHeight="1">
       <c r="A26" s="28" t="inlineStr">
         <is>
-          <t>PROPOSED_AMT</t>
+          <t>SUB_PRODUCT_CODE</t>
         </is>
       </c>
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>NUMBER(20,2)</t>
+          <t>VARCHAR2(100)</t>
         </is>
       </c>
       <c r="C26" s="26" t="inlineStr">
         <is>
-          <t>Số tiền đề xuất</t>
+          <t>Mã sản phẩm nhánh</t>
         </is>
       </c>
       <c r="D26" s="54" t="inlineStr">
         <is>
-          <t>Số tiền đề xuất</t>
+          <t>CỘT MỚI — BK cạnh SK: Mã sản phẩm nhánh (BK thật của DIM_CLOS_PRODUCT layer Sub Product, UNIQUE toàn cục — khác SUB_PRODUCT_NAME dùng làm điều kiện JOIN)</t>
         </is>
       </c>
       <c r="E26" s="31" t="inlineStr">
         <is>
-          <t>J.PRECREDITLIMIT</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
+          <t>E.SUB_PRODUCT_CODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="60" customHeight="1">
       <c r="A27" s="28" t="inlineStr">
         <is>
-          <t>CREDIT_LIMIT_APPROVAL</t>
+          <t>COMPANY_SK</t>
         </is>
       </c>
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>NUMBER(20,2)</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="C27" s="26" t="inlineStr">
         <is>
-          <t>Hạn mức chuyên gia phê duyệt</t>
+          <t>Khóa đơn vị kinh doanh</t>
         </is>
       </c>
       <c r="D27" s="54" t="inlineStr">
         <is>
-          <t>Hạn mức do chuyên gia phê duyệt</t>
+          <t>Khóa ngoại — tra DIM_LOS_COMPANY. Lookup theo layer Company (COMPANY_EFF_DATE/COMPANY_EXP_DATE), thay cho EFF_DATE/EXP_DATE chung cũ — DIM_LOS_COMPANY tách 3 layer SCD2 độc lập. Mặc định -1 nếu không khớp.</t>
         </is>
       </c>
       <c r="E27" s="31" t="inlineStr">
         <is>
-          <t>K.CREDIT_LIMIT</t>
+          <t>G.DIMENSION_KEY</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="28" t="inlineStr">
         <is>
-          <t>APPROVED_AMT_FINAL</t>
+          <t>COMPANY_CODE</t>
         </is>
       </c>
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>NUMBER(20,2)</t>
+          <t>VARCHAR2(50)</t>
         </is>
       </c>
       <c r="C28" s="26" t="inlineStr">
         <is>
-          <t>Hạn mức phê duyệt cuối cùng</t>
+          <t>Mã đơn vị kinh doanh</t>
         </is>
       </c>
       <c r="D28" s="54" t="inlineStr">
         <is>
-          <t>Hạn mức phê duyệt cuối cùng (BC1.LOAN_AMOUNT, BC3.CREDIT_LIMIT)</t>
+          <t>CỘT MỚI — BK cạnh SK: Mã đơn vị kinh doanh (BK của DIM_LOS_COMPANY layer Company)</t>
         </is>
       </c>
       <c r="E28" s="31" t="inlineStr">
         <is>
-          <t>J.CREDIT_LIMIT</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1">
+          <t>F.COMPANY_CODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">
       <c r="A29" s="28" t="inlineStr">
         <is>
-          <t>APPROVED_TERM</t>
+          <t>CUSTOMER_SK</t>
         </is>
       </c>
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>NVARCHAR2(100)</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="C29" s="26" t="inlineStr">
         <is>
-          <t>Kỳ hạn phê duyệt</t>
+          <t>Khóa khách hàng</t>
         </is>
       </c>
       <c r="D29" s="54" t="inlineStr">
         <is>
-          <t>Kỳ hạn phê duyệt, giữ nguyên văn gốc vì có giá trị không ép được sang số</t>
+          <t>Khóa ngoại — tra DIM_CLOS_CUSTOMER. Đây là chân khách hàng LOS — khác T24_CUSTOMER_SK. Quan hệ N:1 (nhiều hồ sơ/DAYID của cùng khách hàng có thể trỏ cùng 1 CUSTOMER_SK). Mặc định -1 nếu không khớp</t>
         </is>
       </c>
       <c r="E29" s="31" t="inlineStr">
         <is>
-          <t>J.CREDIT_TERM</t>
+          <t>H.DIMENSION_KEY</t>
         </is>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="28" t="inlineStr">
         <is>
-          <t>INTEREST_RATE_PCT</t>
+          <t>CUSTOMER_CODE</t>
         </is>
       </c>
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>NVARCHAR2(500)</t>
+          <t>VARCHAR2(100)</t>
         </is>
       </c>
       <c r="C30" s="26" t="inlineStr">
         <is>
-          <t>Lãi suất phê duyệt</t>
+          <t>Mã khách hàng</t>
         </is>
       </c>
       <c r="D30" s="54" t="inlineStr">
         <is>
-          <t>Lãi suất phê duyệt (%), giữ nguyên văn gốc vì có giá trị không ép được sang số (ví dụ 'Theo thỏa thuận')</t>
+          <t>CỘT MỚI — BK cạnh SK: Mã khách hàng (BK của DIM_CLOS_CUSTOMER)</t>
         </is>
       </c>
       <c r="E30" s="31" t="inlineStr">
         <is>
-          <t>J.INTEREST_RATE</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
+          <t>I.ID_NUMBER</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="105" customHeight="1">
       <c r="A31" s="28" t="inlineStr">
         <is>
-          <t>CURRENCY_CODE</t>
+          <t>PROCESSED_DATE</t>
         </is>
       </c>
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>NVARCHAR2(100)</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="C31" s="26" t="inlineStr">
         <is>
-          <t>Loại tiền</t>
+          <t>Ngày xử lý hồ sơ</t>
         </is>
       </c>
       <c r="D31" s="54" t="inlineStr">
         <is>
-          <t>Loại tiền</t>
+          <t>Ngày xử lý chung của hồ sơ theo 3 mức ưu tiên (phê duyệt cuối / hủy / hoàn tất gần nhất)</t>
         </is>
       </c>
       <c r="E31" s="31" t="inlineStr">
         <is>
-          <t>J.CURRENCY</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="75" customHeight="1">
+          <t>COALESCE((SELECT MAX(D.EXITDATE) FROM D WHERE D.WINAME = A.WI_NAME AND D.WORKSTEP IN ('CreditCommittee','CreditApproval') AND D.DECISION IN ('Send To HOSupport','Reject','Submit','Send To PostSanction','Submit To DisbursementMaker')), (SELECT NVL(D.EXITDATE, D.ENTRYDATE) FROM D WHERE D.WINAME = A.WI_NAME AND D.WORKSTEP = 'CancelRevoke'), (SELECT D.EXITDATE FROM D WHERE D.WINAME = A.WI_NAME AND D.EXITDATE IS NOT NULL ORDER BY D.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY))</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
       <c r="A32" s="28" t="inlineStr">
         <is>
-          <t>APPLICATION_LINK_INFO</t>
+          <t>PROPOSED_AMT</t>
         </is>
       </c>
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(200)</t>
+          <t>NUMBER(20,2)</t>
         </is>
       </c>
       <c r="C32" s="26" t="inlineStr">
         <is>
-          <t>Thông tin liên kết hồ sơ</t>
+          <t>Số tiền đề xuất</t>
         </is>
       </c>
       <c r="D32" s="54" t="inlineStr">
         <is>
-          <t>Thông tin liên kết hồ sơ — cột generic của WFINSTRUMENTTABLE — đổi tên từ VAR_STR12. LEFT JOIN riêng theo WI_NAME=PROCESSINSTANCEID (không lọc CREATEDBY). Dùng làm điều kiện lọc IS NOT NULL cho SLHS_CLOS/SLGN_CLOS (AGG_LOS_KPI_YTD_DAILY)</t>
+          <t>Số tiền đề xuất</t>
         </is>
       </c>
       <c r="E32" s="31" t="inlineStr">
         <is>
-          <t>L.VAR_STR12</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1">
+          <t>J.PRECREDITLIMIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
       <c r="A33" s="28" t="inlineStr">
         <is>
-          <t>LG_REQ</t>
+          <t>CREDIT_LIMIT_APPROVAL</t>
         </is>
       </c>
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(10)</t>
+          <t>NUMBER(20,2)</t>
         </is>
       </c>
       <c r="C33" s="26" t="inlineStr">
         <is>
-          <t>Cờ yêu cầu bảo lãnh</t>
+          <t>Hạn mức chuyên gia phê duyệt</t>
         </is>
       </c>
       <c r="D33" s="54" t="inlineStr">
         <is>
-          <t>Cờ yêu cầu bảo lãnh (Letter of Guarantee) phát sinh theo hồ sơ (boolean true/false). Thiết kế dư thừa</t>
+          <t>Hạn mức do chuyên gia phê duyệt</t>
         </is>
       </c>
       <c r="E33" s="31" t="inlineStr">
         <is>
-          <t>E.LG_REQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
+          <t>K.CREDIT_LIMIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
       <c r="A34" s="28" t="inlineStr">
         <is>
-          <t>FI_REQ</t>
+          <t>APPROVED_AMT_FINAL</t>
         </is>
       </c>
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(10)</t>
+          <t>NUMBER(20,2)</t>
         </is>
       </c>
       <c r="C34" s="26" t="inlineStr">
         <is>
-          <t>Cờ yêu cầu FI</t>
+          <t>Hạn mức phê duyệt cuối</t>
         </is>
       </c>
       <c r="D34" s="54" t="inlineStr">
         <is>
-          <t>Cờ yêu cầu (boolean true/false). Thiết kế dư thừa</t>
+          <t>Hạn mức phê duyệt cuối cùng (BC1.LOAN_AMOUNT, BC3.CREDIT_LIMIT)</t>
         </is>
       </c>
       <c r="E34" s="31" t="inlineStr">
         <is>
-          <t>E.FI_REQ</t>
+          <t>J.CREDIT_LIMIT</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" s="28" t="inlineStr">
         <is>
+          <t>APPROVED_TERM</t>
+        </is>
+      </c>
+      <c r="B35" s="25" t="inlineStr">
+        <is>
+          <t>NVARCHAR2(100)</t>
+        </is>
+      </c>
+      <c r="C35" s="26" t="inlineStr">
+        <is>
+          <t>Kỳ hạn phê duyệt</t>
+        </is>
+      </c>
+      <c r="D35" s="54" t="inlineStr">
+        <is>
+          <t>Kỳ hạn phê duyệt, giữ nguyên văn gốc vì có giá trị không ép được sang số</t>
+        </is>
+      </c>
+      <c r="E35" s="31" t="inlineStr">
+        <is>
+          <t>J.CREDIT_TERM</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="28" t="inlineStr">
+        <is>
+          <t>INTEREST_RATE_PCT</t>
+        </is>
+      </c>
+      <c r="B36" s="25" t="inlineStr">
+        <is>
+          <t>NVARCHAR2(500)</t>
+        </is>
+      </c>
+      <c r="C36" s="26" t="inlineStr">
+        <is>
+          <t>Lãi suất phê duyệt</t>
+        </is>
+      </c>
+      <c r="D36" s="54" t="inlineStr">
+        <is>
+          <t>Lãi suất phê duyệt (%), giữ nguyên văn gốc vì có giá trị không ép được sang số (ví dụ 'Theo thỏa thuận')</t>
+        </is>
+      </c>
+      <c r="E36" s="31" t="inlineStr">
+        <is>
+          <t>J.INTEREST_RATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="28" t="inlineStr">
+        <is>
+          <t>CURRENCY_CODE</t>
+        </is>
+      </c>
+      <c r="B37" s="25" t="inlineStr">
+        <is>
+          <t>NVARCHAR2(100)</t>
+        </is>
+      </c>
+      <c r="C37" s="26" t="inlineStr">
+        <is>
+          <t>Loại tiền</t>
+        </is>
+      </c>
+      <c r="D37" s="54" t="inlineStr">
+        <is>
+          <t>Loại tiền</t>
+        </is>
+      </c>
+      <c r="E37" s="31" t="inlineStr">
+        <is>
+          <t>J.CURRENCY</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="75" customHeight="1">
+      <c r="A38" s="28" t="inlineStr">
+        <is>
+          <t>APPLICATION_LINK_INFO</t>
+        </is>
+      </c>
+      <c r="B38" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(200)</t>
+        </is>
+      </c>
+      <c r="C38" s="26" t="inlineStr">
+        <is>
+          <t>Thông tin liên kết hồ sơ</t>
+        </is>
+      </c>
+      <c r="D38" s="54" t="inlineStr">
+        <is>
+          <t>Thông tin liên kết hồ sơ — cột generic của WFINSTRUMENTTABLE — đổi tên từ VAR_STR12. LEFT JOIN riêng theo WI_NAME=PROCESSINSTANCEID (không lọc CREATEDBY). Dùng làm điều kiện lọc IS NOT NULL cho SLHS_CLOS/SLGN_CLOS (AGG_LOS_KPI_YTD_DAILY)</t>
+        </is>
+      </c>
+      <c r="E38" s="31" t="inlineStr">
+        <is>
+          <t>L.VAR_STR12</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="28" t="inlineStr">
+        <is>
+          <t>LG_REQ</t>
+        </is>
+      </c>
+      <c r="B39" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(10)</t>
+        </is>
+      </c>
+      <c r="C39" s="26" t="inlineStr">
+        <is>
+          <t>Cờ yêu cầu bảo lãnh</t>
+        </is>
+      </c>
+      <c r="D39" s="54" t="inlineStr">
+        <is>
+          <t>Cờ yêu cầu bảo lãnh (Letter of Guarantee) phát sinh theo hồ sơ (boolean true/false)</t>
+        </is>
+      </c>
+      <c r="E39" s="31" t="inlineStr">
+        <is>
+          <t>F.LG_REQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" s="28" t="inlineStr">
+        <is>
+          <t>FI_REQ</t>
+        </is>
+      </c>
+      <c r="B40" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(10)</t>
+        </is>
+      </c>
+      <c r="C40" s="26" t="inlineStr">
+        <is>
+          <t>Cờ yêu cầu FI</t>
+        </is>
+      </c>
+      <c r="D40" s="54" t="inlineStr">
+        <is>
+          <t>Cờ yêu cầu (boolean true/false)</t>
+        </is>
+      </c>
+      <c r="E40" s="31" t="inlineStr">
+        <is>
+          <t>F.FI_REQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" s="28" t="inlineStr">
+        <is>
           <t>PHONE_REQ</t>
         </is>
       </c>
-      <c r="B35" s="25" t="inlineStr">
+      <c r="B41" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C35" s="26" t="inlineStr">
-        <is>
-          <t>Cờ yêu cầu xác minh ĐT</t>
-        </is>
-      </c>
-      <c r="D35" s="54" t="inlineStr">
-        <is>
-          <t>Cờ yêu cầu xác minh điện thoại (boolean true/false). Thiết kế dư thừa</t>
-        </is>
-      </c>
-      <c r="E35" s="31" t="inlineStr">
-        <is>
-          <t>E.PHONE_REQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="75" customHeight="1">
-      <c r="A36" s="28" t="inlineStr">
+      <c r="C41" s="26" t="inlineStr">
+        <is>
+          <t>Cờ yêu cầu xác minh điện thoại</t>
+        </is>
+      </c>
+      <c r="D41" s="54" t="inlineStr">
+        <is>
+          <t>Cờ yêu cầu xác minh điện thoại (boolean true/false)</t>
+        </is>
+      </c>
+      <c r="E41" s="31" t="inlineStr">
+        <is>
+          <t>F.PHONE_REQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" s="28" t="inlineStr">
         <is>
           <t>CHANGE_REQUEST</t>
         </is>
       </c>
-      <c r="B36" s="25" t="inlineStr">
+      <c r="B42" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(200)</t>
         </is>
       </c>
-      <c r="C36" s="26" t="inlineStr">
+      <c r="C42" s="26" t="inlineStr">
         <is>
           <t>Yêu cầu điều chỉnh hồ sơ</t>
         </is>
       </c>
-      <c r="D36" s="54" t="inlineStr">
-        <is>
-          <t>Yêu cầu điều chỉnh hồ sơ — nguồn NG_SB_CLOS_CHANGEREQ.CHANGE_REQUEST. Chuyển từ DIM_CLOS_APPLICATION sang đây (đối chiếu SRS BC2) — bản chất thay đổi thường xuyên theo hồ sơ, không phù hợp cột ổn định SCD2 của DIM, giống cách RLOS đã làm</t>
-        </is>
-      </c>
-      <c r="E36" s="31" t="inlineStr">
+      <c r="D42" s="54" t="inlineStr">
+        <is>
+          <t>Yêu cầu điều chỉnh hồ sơ — nguồn M.CHANGE_REQUEST</t>
+        </is>
+      </c>
+      <c r="E42" s="31" t="inlineStr">
         <is>
           <t>M.CHANGE_REQUEST</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="75" customHeight="1">
-      <c r="A37" s="28" t="inlineStr">
+    <row r="43" ht="45" customHeight="1">
+      <c r="A43" s="28" t="inlineStr">
         <is>
           <t>CHANGE_TYPE</t>
         </is>
       </c>
-      <c r="B37" s="25" t="inlineStr">
+      <c r="B43" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(500)</t>
         </is>
       </c>
-      <c r="C37" s="26" t="inlineStr">
-        <is>
-          <t>Loại thay đổi điều kiện phê duyệt</t>
-        </is>
-      </c>
-      <c r="D37" s="54" t="inlineStr">
-        <is>
-          <t>Loại thay đổi điều kiện phê duyệt, giữ nguyên chuỗi gốc kể cả dạng đa giá trị nối bằng dấu '~' — nguồn NG_SB_CLOS_CHANGEREQ.CHANGE_TYPE, giữ nguyên văn không qua bảng danh mục nào (khác RLOS có DIM_RLOS_CHANGE_TYPE)</t>
-        </is>
-      </c>
-      <c r="E37" s="31" t="inlineStr">
+      <c r="C43" s="26" t="inlineStr">
+        <is>
+          <t>Loại thay đổi điều kiện</t>
+        </is>
+      </c>
+      <c r="D43" s="54" t="inlineStr">
+        <is>
+          <t>Loại thay đổi điều kiện phê duyệt, giữ nguyên chuỗi gốc kể cả dạng đa giá trị nối bằng dấu '~' — nguồn M.CHANGE_TYPE, giữ nguyên văn không qua bảng danh mục nào (khác RLOS có DIM_RLOS_CHANGE_TYPE)</t>
+        </is>
+      </c>
+      <c r="E43" s="31" t="inlineStr">
         <is>
           <t>M.CHANGE_TYPE</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="10" t="n"/>
-      <c r="B39" s="10" t="n"/>
-      <c r="C39" s="10" t="n"/>
-      <c r="D39" s="55" t="inlineStr">
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="10" t="n"/>
+      <c r="B45" s="10" t="n"/>
+      <c r="C45" s="10" t="n"/>
+      <c r="D45" s="55" t="inlineStr">
         <is>
           <t>Điều kiện join giữa các bảng</t>
         </is>
       </c>
-      <c r="E39" s="10" t="n"/>
-    </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="25" t="n"/>
-      <c r="B40" s="25" t="n"/>
-      <c r="C40" s="51" t="n"/>
-      <c r="D40" s="54" t="n"/>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t>LEFT JOIN B.WI_NAME = A.WI_NAME AND v_batch_date BETWEEN B.EFF_DATE AND NVL(B.EXP_DATE, v_batch_date)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="45" customHeight="1">
-      <c r="A41" s="25" t="n"/>
-      <c r="B41" s="25" t="n"/>
-      <c r="C41" s="51" t="n"/>
-      <c r="D41" s="54" t="n"/>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>LEFT JOIN (SELECT C.WORKSTEP, C.DECISION FROM C WHERE C.WINAME = A.WI_NAME AND C.EXITDATE IS NOT NULL AND C.ENTRYDATE &lt;= v_batch_date ORDER BY C.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY) LAST_EVENT ON 1=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="45" customHeight="1">
-      <c r="A42" s="25" t="n"/>
-      <c r="B42" s="25" t="n"/>
-      <c r="C42" s="51" t="n"/>
-      <c r="D42" s="54" t="n"/>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t>LEFT JOIN D.WORKSTEP_CODE = LAST_EVENT.WORKSTEP AND D.DECISION_CODE = LAST_EVENT.DECISION AND v_batch_date BETWEEN D.EFF_DATE AND NVL(D.EXP_DATE, v_batch_date)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="25" t="n"/>
-      <c r="B43" s="25" t="n"/>
-      <c r="C43" s="51" t="n"/>
-      <c r="D43" s="54" t="n"/>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t>LEFT JOIN E.WI_NAME = A.WI_NAME</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="25" t="n"/>
-      <c r="B44" s="25" t="n"/>
-      <c r="C44" s="51" t="n"/>
-      <c r="D44" s="54" t="n"/>
-      <c r="E44" s="8" t="inlineStr">
-        <is>
-          <t>LEFT JOIN F.PRODUCTLINE_CODE = E.PRODUCT_LINE AND v_batch_date BETWEEN F.PRODUCTLINE_EFF_DATE AND NVL(F.PRODUCTLINE_EXP_DATE, v_batch_date)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="25" t="n"/>
-      <c r="B45" s="25" t="n"/>
-      <c r="C45" s="51" t="n"/>
-      <c r="D45" s="54" t="n"/>
-      <c r="E45" s="8" t="inlineStr">
-        <is>
-          <t>LEFT JOIN F.SUB_PRODUCT_NAME = E.SUB_PRODUCT AND v_batch_date BETWEEN F.SUB_PRODUCT_EFF_DATE AND NVL(F.SUB_PRODUCT_EXP_DATE, v_batch_date)</t>
-        </is>
-      </c>
+      <c r="E45" s="10" t="n"/>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="25" t="n"/>
@@ -1563,7 +1659,7 @@
       <c r="D46" s="54" t="n"/>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>LEFT JOIN G.COMPANY_CODE = E.COMPANY_CODE AND v_batch_date BETWEEN G.COMPANY_EFF_DATE AND NVL(G.COMPANY_EXP_DATE, v_batch_date)</t>
+          <t>LEFT JOIN B.WI_NAME = A.WI_NAME AND v_batch_date BETWEEN B.EFF_DATE AND NVL(B.EXP_DATE, v_batch_date)</t>
         </is>
       </c>
     </row>
@@ -1574,18 +1670,18 @@
       <c r="D47" s="54" t="n"/>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>LEFT JOIN H.WI_NAME = A.WI_NAME AND UPPER(H.OBJ_TYPE) = 'KHÁCH HÀNG' AND ROW_NUMBER() OVER (PARTITION BY H.WI_NAME ORDER BY H.RECID DESC) = 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="30" customHeight="1">
+          <t>LEFT JOIN (SELECT D.WORKSTEP, D.DECISION FROM D WHERE D.WINAME = A.WI_NAME AND D.EXITDATE IS NOT NULL AND D.ENTRYDATE &lt;= v_batch_date ORDER BY D.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY) LAST_EVENT ON 1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="45" customHeight="1">
       <c r="A48" s="25" t="n"/>
       <c r="B48" s="25" t="n"/>
       <c r="C48" s="51" t="n"/>
       <c r="D48" s="54" t="n"/>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>LEFT JOIN I.CUSTOMER_CODE = H.ID_NUMBER AND v_batch_date BETWEEN I.EFF_DATE AND NVL(I.EXP_DATE, v_batch_date)</t>
+          <t>LEFT JOIN C.WORKSTEP_CODE = LAST_EVENT.WORKSTEP AND C.DECISION_CODE = LAST_EVENT.DECISION AND v_batch_date BETWEEN C.EFF_DATE AND NVL(C.EXP_DATE, v_batch_date)</t>
         </is>
       </c>
     </row>
@@ -1596,18 +1692,18 @@
       <c r="D49" s="54" t="n"/>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>LEFT JOIN J.WI_NAME = A.WI_NAME</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="15" customHeight="1">
+          <t>LEFT JOIN F.WI_NAME = A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
       <c r="A50" s="25" t="n"/>
       <c r="B50" s="25" t="n"/>
       <c r="C50" s="51" t="n"/>
       <c r="D50" s="54" t="n"/>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>LEFT JOIN K.WI_NAME = A.WI_NAME</t>
+          <t>LEFT JOIN E.PRODUCTLINE_CODE = F.PRODUCT_LINE AND v_batch_date BETWEEN E.PRODUCTLINE_EFF_DATE AND NVL(E.PRODUCTLINE_EXP_DATE, v_batch_date)</t>
         </is>
       </c>
     </row>
@@ -1618,16 +1714,82 @@
       <c r="D51" s="54" t="n"/>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>LEFT JOIN L.PROCESSINSTANCEID = A.WI_NAME AND ROW_NUMBER() OVER (PARTITION BY L.PROCESSINSTANCEID ORDER BY L.CREATEDBY) = 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="15" customHeight="1">
+          <t>LEFT JOIN E.SUB_PRODUCT_NAME = F.SUB_PRODUCT AND v_batch_date BETWEEN E.SUB_PRODUCT_EFF_DATE AND NVL(E.SUB_PRODUCT_EXP_DATE, v_batch_date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
       <c r="A52" s="25" t="n"/>
       <c r="B52" s="25" t="n"/>
       <c r="C52" s="51" t="n"/>
       <c r="D52" s="54" t="n"/>
       <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN G.COMPANY_CODE = F.COMPANY_CODE AND v_batch_date BETWEEN G.COMPANY_EFF_DATE AND NVL(G.COMPANY_EXP_DATE, v_batch_date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="45" customHeight="1">
+      <c r="A53" s="25" t="n"/>
+      <c r="B53" s="25" t="n"/>
+      <c r="C53" s="51" t="n"/>
+      <c r="D53" s="54" t="n"/>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN I.WI_NAME = A.WI_NAME AND UPPER(I.OBJ_TYPE) = 'KHÁCH HÀNG' AND ROW_NUMBER() OVER (PARTITION BY I.WI_NAME ORDER BY I.RECID DESC) = 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="25" t="n"/>
+      <c r="B54" s="25" t="n"/>
+      <c r="C54" s="51" t="n"/>
+      <c r="D54" s="54" t="n"/>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN H.CUSTOMER_CODE = I.ID_NUMBER AND v_batch_date BETWEEN H.EFF_DATE AND NVL(H.EXP_DATE, v_batch_date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="A55" s="25" t="n"/>
+      <c r="B55" s="25" t="n"/>
+      <c r="C55" s="51" t="n"/>
+      <c r="D55" s="54" t="n"/>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN J.WI_NAME = A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="A56" s="25" t="n"/>
+      <c r="B56" s="25" t="n"/>
+      <c r="C56" s="51" t="n"/>
+      <c r="D56" s="54" t="n"/>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN K.WI_NAME = A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="25" t="n"/>
+      <c r="B57" s="25" t="n"/>
+      <c r="C57" s="51" t="n"/>
+      <c r="D57" s="54" t="n"/>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN L.PROCESSINSTANCEID = A.WI_NAME AND ROW_NUMBER() OVER (PARTITION BY L.PROCESSINSTANCEID ORDER BY CREATEDBY) = 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" s="25" t="n"/>
+      <c r="B58" s="25" t="n"/>
+      <c r="C58" s="51" t="n"/>
+      <c r="D58" s="54" t="n"/>
+      <c r="E58" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN M.WI_NAME = A.WI_NAME</t>
         </is>
